--- a/src/main/resources/client-labels/apc-etiquetas-wh-crosslog.xlsx
+++ b/src/main/resources/client-labels/apc-etiquetas-wh-crosslog.xlsx
@@ -3,19 +3,23 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\documentos\ETIQUETAS\APC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\system.PUNTOTRES\Documents\WORKSPACE\PackingListAutomation\target\muestras-etiquetas-apc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E94E590-B2D0-4022-A94C-72506166D0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F4A426-0542-44F5-B665-E2EF554C2F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="857" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="857" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Etiquette colis Crosslog" sheetId="1" r:id="rId1"/>
     <sheet name="Etiquette Palette Crosslog" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Etiquette colis Crosslog'!$A$1:$D$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Etiquette Palette Crosslog'!$A$1:$B$26</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="36">
   <si>
     <r>
       <t xml:space="preserve">DESTINATAIRE
@@ -116,22 +120,6 @@
   </si>
   <si>
     <t xml:space="preserve">Pieces by size : </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Nombre total de colis sur la palette
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial Black"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Total number of packages on the palette)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -208,19 +196,70 @@
     <t xml:space="preserve">, </t>
   </si>
   <si>
-    <t>PXCBS-F67066</t>
-  </si>
-  <si>
-    <t>PUN20260717WH1</t>
-  </si>
-  <si>
     <t>LZZ-NOIR</t>
   </si>
   <si>
-    <t>89 / 89</t>
-  </si>
-  <si>
-    <t>3,00 kg</t>
+    <t>EXPEDITEUR
+(Shipper / Sender)
+-
+PROVENANCE
+(Origin)</t>
+  </si>
+  <si>
+    <t>DESTINATAIRE
+(Consignee)</t>
+  </si>
+  <si>
+    <t>DESTINATION
+(Destination)</t>
+  </si>
+  <si>
+    <t>4100128863</t>
+  </si>
+  <si>
+    <t>PUN20260928WH1</t>
+  </si>
+  <si>
+    <t>PXCBC-F67008</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>1 / 3</t>
+  </si>
+  <si>
+    <t>7,60 Kg</t>
+  </si>
+  <si>
+    <t>Nombre total de colis sur la palette
+(Total number of packages on the palette)</t>
+  </si>
+  <si>
+    <t>Poids brut 
+(Total gross weight)</t>
+  </si>
+  <si>
+    <t>25,20 Kg</t>
+  </si>
+  <si>
+    <t>16,20 Kg</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nombre total de colis sur la palette
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Black"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Total number of packages on the palette)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -272,19 +311,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial Black"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial Black"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial Black"/>
@@ -296,6 +322,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -381,8 +420,8 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -434,9 +473,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -450,6 +486,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -475,15 +514,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2873375</xdr:colOff>
+      <xdr:colOff>3131111</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
+      <xdr:rowOff>22412</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>502957</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>94901</xdr:rowOff>
+      <xdr:colOff>760693</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>35884</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -513,8 +552,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3175000" y="158750"/>
-          <a:ext cx="1874557" cy="602901"/>
+          <a:off x="3478493" y="22412"/>
+          <a:ext cx="1674906" cy="674619"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -536,9 +575,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2873375</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>3187140</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>100854</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1677707" cy="672751"/>
     <xdr:pic>
@@ -569,7 +608,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3159125" y="158750"/>
+          <a:off x="3534522" y="8169089"/>
           <a:ext cx="1677707" cy="672751"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -596,16 +635,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2746375</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2413000</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>601382</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>47276</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>791882</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>94901</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -635,8 +674,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3048000" y="142875"/>
-          <a:ext cx="1868207" cy="606076"/>
+          <a:off x="2413000" y="342900"/>
+          <a:ext cx="1693582" cy="666401"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -651,6 +690,50 @@
             </a14:hiddenFill>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2374900</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>753782</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>85376</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2374900" y="6677025"/>
+          <a:ext cx="1693582" cy="666401"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -947,235 +1030,207 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor theme="7" tint="0.39997558519241921"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="3" width="60.7109375" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.28515625"/>
+    <col min="2" max="3" customWidth="true" width="60.7109375"/>
+    <col min="4" max="4" customWidth="true" width="5.28515625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="2.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
+    <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B4" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="17"/>
+    </row>
+    <row r="5" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="18"/>
-    </row>
-    <row r="7" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="19" t="s">
+      <c r="C5" s="18"/>
+    </row>
+    <row r="6" spans="1:3" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:3" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="90.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="19"/>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:3" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="8" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="59.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="32.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" spans="1:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="5"/>
+    </row>
+    <row r="13" spans="1:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="5"/>
+    </row>
+    <row r="14" spans="1:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A14" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="5"/>
+    </row>
+    <row r="15" spans="1:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6"/>
+    </row>
+    <row r="16" spans="1:3" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="15"/>
+    </row>
+    <row r="19" spans="2:3" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="2:3" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B23" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="90.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="9" t="s">
+      <c r="C23" s="17"/>
+    </row>
+    <row r="24" spans="2:3" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="18"/>
+    </row>
+    <row r="25" spans="2:3" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="2:3" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" ht="81.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="59.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="9" t="s">
+      <c r="C27" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C28" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="32.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="10" t="s">
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B30" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="4">
-        <v>4100128725</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="11" t="s">
+      <c r="C30" s="4"/>
+    </row>
+    <row r="31" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B31" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="11" t="s">
+      <c r="C31" s="5"/>
+    </row>
+    <row r="32" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B32" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="11" t="s">
+      <c r="C32" s="5"/>
+    </row>
+    <row r="33" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="B33" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="12" t="s">
+      <c r="C33" s="5"/>
+    </row>
+    <row r="34" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C34" s="6"/>
+    </row>
+    <row r="35" spans="2:3" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="13" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="2:3" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="2"/>
-    </row>
-    <row r="19" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B26" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="18"/>
-    </row>
-    <row r="27" spans="2:3" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="19"/>
-    </row>
-    <row r="28" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="2:3" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" ht="81.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B33" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C33" s="4">
-        <v>4100128725</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B34" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B35" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B36" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="2"/>
-    </row>
-    <row r="39" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>26</v>
-      </c>
+      <c r="C37" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="63" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="67" fitToWidth="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -1184,82 +1239,74 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="7" tint="0.39997558519241921"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:D14"/>
+  <dimension ref="A4:B13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="3" width="57.5703125" customWidth="1"/>
+    <col min="1" max="2" customWidth="true" width="49.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="D1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
+    <row r="4" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="17"/>
+    </row>
+    <row r="5" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="18"/>
-    </row>
-    <row r="7" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="19" t="s">
+      <c r="B5" s="18"/>
+    </row>
+    <row r="6" spans="1:2" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:2" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="93.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="19"/>
-    </row>
-    <row r="8" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="2:4" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" ht="93.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="2"/>
-    </row>
-    <row r="13" spans="2:4" ht="45.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="14" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="25.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="11" spans="1:2" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="7"/>
+    </row>
+    <row r="12" spans="1:2" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="17">
-        <v>55.4</v>
-      </c>
-    </row>
+      <c r="B12" s="16"/>
+    </row>
+    <row r="13" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
+  <mergeCells count="4">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="82" fitToWidth="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>